--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010715</t>
+          <t xml:space="preserve">200010720</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -15964,12 +15964,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419877</t>
+          <t xml:space="preserve">311419878</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311420218</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">

--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>788</v>
+        <v>1856</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389420</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J204">
-        <v>1856</v>
+        <v>2960</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>2960</v>
+        <v>1091</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15431,11 +15431,11 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J206">
-        <v>1091</v>
+        <v>380</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15506,11 +15506,11 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J207">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15581,11 +15581,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J208">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Tøstrupvej 26</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>447</v>
+        <v>2185</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøstrupvej 26</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>2185</v>
+        <v>655</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15806,11 +15806,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Engdraget 24A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,21 +15885,21 @@
         </is>
       </c>
       <c r="J212">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311419880</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 24A</t>
+          <t xml:space="preserve">Engdraget 26A</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J213">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419878</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 26A</t>
+          <t xml:space="preserve">Skjernåvej 4A</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,30 +16026,30 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420218</t>
+          <t xml:space="preserve">311424140</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjernåvej 4A</t>
+          <t xml:space="preserve">Svinget 5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,21 +16110,21 @@
         </is>
       </c>
       <c r="J215">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424140</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J216">
-        <v>392</v>
+        <v>703</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 5</t>
+          <t xml:space="preserve">Centerparken 1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">9701346</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>703</v>
+        <v>4482</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311552774</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centerparken 1</t>
+          <t xml:space="preserve">Jægervej 13</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9701346</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>4482</v>
+        <v>1557</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552774</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-04</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 13</t>
+          <t xml:space="preserve">Lærkevænget 1</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>1557</v>
+        <v>417</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevænget 1</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>417</v>
+        <v>1060</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311555859</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,17 +16541,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>1060</v>
+        <v>606</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555859</t>
+          <t xml:space="preserve">311561693</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Storegade 40</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4467758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>606</v>
+        <v>401</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561693</t>
+          <t xml:space="preserve">311599352</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-13</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,17 +16691,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40</t>
+          <t xml:space="preserve">Åvænget 3A</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467758</t>
+          <t xml:space="preserve">100145225</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>401</v>
+        <v>810</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599352</t>
+          <t xml:space="preserve">311582272</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åvænget 3A</t>
+          <t xml:space="preserve">Nygade 1</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100145225</t>
+          <t xml:space="preserve">4467959</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16785,11 +16785,11 @@
         </is>
       </c>
       <c r="J224">
-        <v>810</v>
+        <v>308</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582272</t>
+          <t xml:space="preserve">311598466</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,17 +16841,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 1</t>
+          <t xml:space="preserve">Midtbyvej 30</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467959</t>
+          <t xml:space="preserve">7662602</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,21 +16860,21 @@
         </is>
       </c>
       <c r="J225">
-        <v>308</v>
+        <v>1817</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598466</t>
+          <t xml:space="preserve">311650708</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">MST-Bygtjek ApS</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,40 +16916,40 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 30</t>
+          <t xml:space="preserve">Ranunkelvej 11A</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7662602</t>
+          <t xml:space="preserve">5790131, 100782857</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J226">
-        <v>1817</v>
+        <v>414</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650708</t>
+          <t xml:space="preserve">311689382</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">MST-Bygtjek ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,40 +16991,40 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 11A</t>
+          <t xml:space="preserve">Skolebakken 20</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131, 100782857</t>
+          <t xml:space="preserve">746445, 4419703</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J227">
-        <v>414</v>
+        <v>3326</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689382</t>
+          <t xml:space="preserve">311883390</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2036-02-21</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 20</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">746445, 4419703</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>3326</v>
+        <v>1345</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883390</t>
+          <t xml:space="preserve">311886105</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-21</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17156,15 +17156,15 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J229">
-        <v>1345</v>
+        <v>2810</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886105</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17231,15 +17231,15 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J230">
-        <v>2810</v>
+        <v>1725</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311886107</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17306,15 +17306,15 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J231">
-        <v>1725</v>
+        <v>1360</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886107</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,21 +17385,21 @@
         </is>
       </c>
       <c r="J232">
-        <v>1360</v>
+        <v>703</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311889055</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,40 +17441,40 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J233">
-        <v>703</v>
+        <v>766</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311889055</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,30 +17516,30 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>766</v>
+        <v>2123</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J235">
-        <v>2123</v>
+        <v>915</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J236">
-        <v>915</v>
+        <v>616</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17756,11 +17756,11 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J237">
-        <v>616</v>
+        <v>1810</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17816,35 +17816,35 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">746506, 4477641</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J238">
-        <v>1810</v>
+        <v>2072</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892347</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -17891,17 +17891,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Ågade 12</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">746506, 4477641</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,16 +17910,16 @@
         </is>
       </c>
       <c r="J239">
-        <v>2072</v>
+        <v>729</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892347</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 12</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
@@ -18041,17 +18041,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Badevej 17A</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">4421290, 100992804</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,21 +18060,21 @@
         </is>
       </c>
       <c r="J241">
-        <v>729</v>
+        <v>370</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311900271</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-05-10</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,40 +18116,40 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Badevej 17A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421290, 100992804</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J242">
-        <v>370</v>
+        <v>788</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900271</t>
+          <t xml:space="preserve">311929041</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-10</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">

--- a/public/exports/29189609.xlsx
+++ b/public/exports/29189609.xlsx
@@ -5366,26 +5366,26 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Klostervej 3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746264, 4471745</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>735</v>
+        <v>1396</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5456,11 +5456,11 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J73">
-        <v>1396</v>
+        <v>320</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,26 +5516,26 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 3</t>
+          <t xml:space="preserve">Klostervej 65</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">746264, 4471745</t>
+          <t xml:space="preserve">8427851</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J74">
-        <v>320</v>
+        <v>2567</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J75">
-        <v>2567</v>
+        <v>380</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 65</t>
+          <t xml:space="preserve">Klostervej 67A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>380</v>
+        <v>8744</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>8744</v>
+        <v>1430</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,26 +5816,26 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 67A</t>
+          <t xml:space="preserve">Kroghedevej 2A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427851</t>
+          <t xml:space="preserve">746603, 10238250</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J78">
-        <v>1430</v>
+        <v>1035</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J79">
-        <v>1035</v>
+        <v>339</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,26 +5966,26 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kroghedevej 2A</t>
+          <t xml:space="preserve">Lybækvej 14A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">746603, 10238250</t>
+          <t xml:space="preserve">10009013</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>339</v>
+        <v>406</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6041,26 +6041,26 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lybækvej 14A</t>
+          <t xml:space="preserve">Lønborgvej 53</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10009013</t>
+          <t xml:space="preserve">4468195</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J81">
-        <v>406</v>
+        <v>5216</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6116,17 +6116,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønborgvej 53</t>
+          <t xml:space="preserve">Mellemgade 23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468195</t>
+          <t xml:space="preserve">8570394</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="J82">
-        <v>5216</v>
+        <v>664</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,17 +6191,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 23</t>
+          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8570394</t>
+          <t xml:space="preserve">746733, 9329112</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="J83">
-        <v>664</v>
+        <v>765</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,26 +6266,26 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Søndergårdsvej 1</t>
+          <t xml:space="preserve">Nygade 48</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">746733, 9329112</t>
+          <t xml:space="preserve">100098945</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>765</v>
+        <v>1535</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 48</t>
+          <t xml:space="preserve">Nygade 50A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,16 +6351,16 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">100098945</t>
+          <t xml:space="preserve">100287180</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>1535</v>
+        <v>340</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6416,17 +6416,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 50A</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100287180</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="J86">
-        <v>340</v>
+        <v>2175</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J87">
-        <v>2175</v>
+        <v>362</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J88">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Nørlundvej 3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">100361476</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="J89">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 3</t>
+          <t xml:space="preserve">Nørlundvej 7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,16 +6726,16 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">100361476</t>
+          <t xml:space="preserve">7879617</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>371</v>
+        <v>635</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,17 +6791,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 7</t>
+          <t xml:space="preserve">Nørregade 84</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7879617</t>
+          <t xml:space="preserve">4416989</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="J91">
-        <v>635</v>
+        <v>855</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 84</t>
+          <t xml:space="preserve">Nørregade 88</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4416989</t>
+          <t xml:space="preserve">746342, 4414222</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="J92">
-        <v>855</v>
+        <v>353</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 88</t>
+          <t xml:space="preserve">Parallelvej 116</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">746342, 4414222</t>
+          <t xml:space="preserve">4417458</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="J93">
-        <v>353</v>
+        <v>262</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J95">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 116</t>
+          <t xml:space="preserve">Parallelvej 301</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,16 +7176,16 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417458</t>
+          <t xml:space="preserve">100060251</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>256</v>
+        <v>1021</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,26 +7241,26 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 301</t>
+          <t xml:space="preserve">Ranunkelvej 1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060251</t>
+          <t xml:space="preserve">746495, 5790131</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J97">
-        <v>1021</v>
+        <v>920</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7331,11 +7331,11 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J98">
-        <v>920</v>
+        <v>2717</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J99">
-        <v>2717</v>
+        <v>1531</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J100">
-        <v>1531</v>
+        <v>3165</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 1</t>
+          <t xml:space="preserve">Ranunkelvej 5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J101">
-        <v>3165</v>
+        <v>740</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 5</t>
+          <t xml:space="preserve">Ranunkelvej 7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,16 +7626,16 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">746495, 5790131</t>
+          <t xml:space="preserve">5790131</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J102">
-        <v>740</v>
+        <v>7967</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,26 +7691,26 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 7</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J103">
-        <v>7967</v>
+        <v>1259</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J104">
-        <v>1259</v>
+        <v>1728</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J105">
-        <v>1728</v>
+        <v>704</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7916,26 +7916,26 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Skolestræde 1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">7155670</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>704</v>
+        <v>472</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>447</v>
+        <v>1502</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J109">
-        <v>1502</v>
+        <v>266</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J110">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,26 +8291,26 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 1</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155670</t>
+          <t xml:space="preserve">4471273</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>273</v>
+        <v>1021</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4471273</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="J112">
-        <v>1021</v>
+        <v>698</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J113">
-        <v>698</v>
+        <v>1606</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J114">
-        <v>1606</v>
+        <v>516</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Skolevænget 31B</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
-        <v>516</v>
+        <v>282</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31B</t>
+          <t xml:space="preserve">Skovvej 29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">100064416</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="J116">
-        <v>282</v>
+        <v>1014</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,26 +8741,26 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 29</t>
+          <t xml:space="preserve">Skyggehusvej 2A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064416</t>
+          <t xml:space="preserve">9177616</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J117">
-        <v>1014</v>
+        <v>2728</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J118">
-        <v>2728</v>
+        <v>1122</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,26 +8891,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyggehusvej 2A</t>
+          <t xml:space="preserve">Smed Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9177616</t>
+          <t xml:space="preserve">8918730</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J119">
-        <v>1122</v>
+        <v>1946</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 1</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,16 +8976,16 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918730</t>
+          <t xml:space="preserve">746471, 5725286</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>1946</v>
+        <v>1793</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9041,26 +9041,26 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3A</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">746471, 5725286</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J121">
-        <v>1793</v>
+        <v>266</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J122">
-        <v>266</v>
+        <v>458</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,26 +9191,26 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J123">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9281,11 +9281,11 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J124">
-        <v>468</v>
+        <v>2597</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,26 +9341,26 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Torvegade 20A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">9037914</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>2597</v>
+        <v>1284</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 20A</t>
+          <t xml:space="preserve">Torvet 22</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9037914</t>
+          <t xml:space="preserve">5724727</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="J126">
-        <v>1284</v>
+        <v>606</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 22</t>
+          <t xml:space="preserve">Tylvadvej 2B</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724727</t>
+          <t xml:space="preserve">746514, 4480243</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="J127">
-        <v>606</v>
+        <v>2572</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J128">
-        <v>2572</v>
+        <v>1285</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2B</t>
+          <t xml:space="preserve">Tylvadvej 2C</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,16 +9651,16 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">746514, 4480243</t>
+          <t xml:space="preserve">746560, 4480243</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>1285</v>
+        <v>294</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2C</t>
+          <t xml:space="preserve">Tømrervej 2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,16 +9726,16 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">746560, 4480243</t>
+          <t xml:space="preserve">5789801</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>294</v>
+        <v>828</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tømrervej 2</t>
+          <t xml:space="preserve">V Strandsbjerg 29</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789801</t>
+          <t xml:space="preserve">746437, 5725570</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="J131">
-        <v>828</v>
+        <v>355</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9866,26 +9866,26 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">V Strandsbjerg 29</t>
+          <t xml:space="preserve">Vardevej 11</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">746437, 5725570</t>
+          <t xml:space="preserve">4469018</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
-        <v>355</v>
+        <v>2841</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J133">
-        <v>2841</v>
+        <v>795</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J134">
-        <v>795</v>
+        <v>2194</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J135">
-        <v>2194</v>
+        <v>825</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10181,11 +10181,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J136">
-        <v>825</v>
+        <v>1037</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 11</t>
+          <t xml:space="preserve">Vardevej 13</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,16 +10251,16 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4469018</t>
+          <t xml:space="preserve">4468945</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J137">
-        <v>1037</v>
+        <v>286</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10316,26 +10316,26 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 13</t>
+          <t xml:space="preserve">Ved Fjorden 2A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468945</t>
+          <t xml:space="preserve">746456, 5725275</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J138">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2A</t>
+          <t xml:space="preserve">Ved Fjorden 2B</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,16 +10401,16 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">746456, 5725275</t>
+          <t xml:space="preserve">746458, 8463679</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J139">
-        <v>268</v>
+        <v>375</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 2B</t>
+          <t xml:space="preserve">Ved Fjorden 6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,16 +10476,16 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">746458, 8463679</t>
+          <t xml:space="preserve">5725532</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>375</v>
+        <v>3304</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Fjorden 6</t>
+          <t xml:space="preserve">Ågade 2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725532</t>
+          <t xml:space="preserve">9221919</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="J141">
-        <v>3304</v>
+        <v>3757</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 2</t>
+          <t xml:space="preserve">Østerbyvej 3B</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,16 +10626,16 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221919</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>3757</v>
+        <v>475</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10691,45 +10691,45 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbyvej 3B</t>
+          <t xml:space="preserve">Ternevej 2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">4480741</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>475</v>
+        <v>2202</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200008078</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">PP Rådgivning A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-10-09</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 2</t>
+          <t xml:space="preserve">Nørrevænget 33</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480741</t>
+          <t xml:space="preserve">8369478</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,21 +10785,21 @@
         </is>
       </c>
       <c r="J144">
-        <v>2202</v>
+        <v>377</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008078</t>
+          <t xml:space="preserve">200010715</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP Rådgivning A/S</t>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-09</t>
+          <t xml:space="preserve">2019-02-18</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 33</t>
+          <t xml:space="preserve">Vasevej 31</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8369478</t>
+          <t xml:space="preserve">5727592</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>377</v>
+        <v>821</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010720</t>
+          <t xml:space="preserve">200010804</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-18</t>
+          <t xml:space="preserve">2019-02-22</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 31</t>
+          <t xml:space="preserve">Søibergsvej 15</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5727592</t>
+          <t xml:space="preserve">5726357</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>821</v>
+        <v>563</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010804</t>
+          <t xml:space="preserve">200010845</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-22</t>
+          <t xml:space="preserve">2019-02-23</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 15</t>
+          <t xml:space="preserve">Vasevej 29</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726357</t>
+          <t xml:space="preserve">5728667</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>563</v>
+        <v>491</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010845</t>
+          <t xml:space="preserve">200010944</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-23</t>
+          <t xml:space="preserve">2019-02-25</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vasevej 29</t>
+          <t xml:space="preserve">Søibergsvej 13</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5728667</t>
+          <t xml:space="preserve">5726356</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>491</v>
+        <v>680</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010944</t>
+          <t xml:space="preserve">200010984</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-25</t>
+          <t xml:space="preserve">2019-02-26</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 13</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726356</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>680</v>
+        <v>403</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010984</t>
+          <t xml:space="preserve">200011840</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-26</t>
+          <t xml:space="preserve">2019-03-25</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Klostervej 33</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">4422741</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011840</t>
+          <t xml:space="preserve">200011821</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 33</t>
+          <t xml:space="preserve">Søibergsvej 11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422741</t>
+          <t xml:space="preserve">5726355</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>390</v>
+        <v>529</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011821</t>
+          <t xml:space="preserve">200011832</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 11</t>
+          <t xml:space="preserve">Godthaabsvej 8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726355</t>
+          <t xml:space="preserve">5725086</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>529</v>
+        <v>746</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011832</t>
+          <t xml:space="preserve">200011892</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-25</t>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,17 +11441,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthaabsvej 8</t>
+          <t xml:space="preserve">Adelvej 39A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725086</t>
+          <t xml:space="preserve">4419782</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,21 +11460,21 @@
         </is>
       </c>
       <c r="J153">
-        <v>746</v>
+        <v>419</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011892</t>
+          <t xml:space="preserve">200012873</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2019-04-27</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelvej 39A</t>
+          <t xml:space="preserve">Holmegaardsbakken 22</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419782</t>
+          <t xml:space="preserve">8161686</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,16 +11535,16 @@
         </is>
       </c>
       <c r="J154">
-        <v>419</v>
+        <v>314</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012873</t>
+          <t xml:space="preserve">200012912</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 22</t>
+          <t xml:space="preserve">Hvidkløvervej 8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8161686</t>
+          <t xml:space="preserve">9430418</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012912</t>
+          <t xml:space="preserve">200012910</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidkløvervej 8</t>
+          <t xml:space="preserve">Herningvej 31</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430418</t>
+          <t xml:space="preserve">5726882</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012910</t>
+          <t xml:space="preserve">200012988</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-27</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 31</t>
+          <t xml:space="preserve">Byskellet 20</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726882</t>
+          <t xml:space="preserve">5725537</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>253</v>
+        <v>1556</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012988</t>
+          <t xml:space="preserve">200013034</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2019-04-29</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byskellet 20</t>
+          <t xml:space="preserve">Drosselvej 9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725537</t>
+          <t xml:space="preserve">5792930</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>1556</v>
+        <v>356</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013034</t>
+          <t xml:space="preserve">200013038</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 9</t>
+          <t xml:space="preserve">Fischersvej 6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792930</t>
+          <t xml:space="preserve">4483012</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>356</v>
+        <v>848</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013038</t>
+          <t xml:space="preserve">200012993</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fischersvej 6</t>
+          <t xml:space="preserve">Rødkløvervej 4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483012</t>
+          <t xml:space="preserve">9379331</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>848</v>
+        <v>1290</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012993</t>
+          <t xml:space="preserve">200013233</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-29</t>
+          <t xml:space="preserve">2019-05-04</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødkløvervej 4</t>
+          <t xml:space="preserve">Klostervej 39</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9379331</t>
+          <t xml:space="preserve">9670777</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>1290</v>
+        <v>2672</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013233</t>
+          <t xml:space="preserve">200014492</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-04</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 39</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9670777</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>2672</v>
+        <v>3316</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014492</t>
+          <t xml:space="preserve">200014523</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2019-06-04</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Kongevejen 1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">5724668</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>3316</v>
+        <v>380</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014523</t>
+          <t xml:space="preserve">200014705</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-04</t>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 1</t>
+          <t xml:space="preserve">Lønhøjvej 38</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724668</t>
+          <t xml:space="preserve">4468081</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>380</v>
+        <v>837</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014705</t>
+          <t xml:space="preserve">200014740</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lønhøjvej 38</t>
+          <t xml:space="preserve">Engdraget 4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468081</t>
+          <t xml:space="preserve">4468323</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>837</v>
+        <v>614</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014740</t>
+          <t xml:space="preserve">200015083</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2019-06-16</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 4</t>
+          <t xml:space="preserve">Parallelvej 100</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468323</t>
+          <t xml:space="preserve">8043441</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>614</v>
+        <v>3650</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015083</t>
+          <t xml:space="preserve">200015550</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-16</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 100</t>
+          <t xml:space="preserve">Nylandsvej 10</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043441</t>
+          <t xml:space="preserve">5788092</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>3650</v>
+        <v>284</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015550</t>
+          <t xml:space="preserve">200016205</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2019-06-29</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,40 +12566,40 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nylandsvej 10</t>
+          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788092</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J168">
-        <v>284</v>
+        <v>995</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016205</t>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-29</t>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J169">
-        <v>995</v>
+        <v>1395</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apoteker Rasmussens Plads 6A</t>
+          <t xml:space="preserve">Kirkegade 3B</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J170">
-        <v>1395</v>
+        <v>2716</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12806,15 +12806,15 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>2716</v>
+        <v>756</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">200033989</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3B</t>
+          <t xml:space="preserve">Kirkegade 5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J172">
-        <v>756</v>
+        <v>1725</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 5</t>
+          <t xml:space="preserve">Kongevejen 52A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">5725835</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>1725</v>
+        <v>2126</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033989</t>
+          <t xml:space="preserve">200054663</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,40 +13016,40 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 52A</t>
+          <t xml:space="preserve">Midtbyvej 32</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725835</t>
+          <t xml:space="preserve">746271, 4473222</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J174">
-        <v>2126</v>
+        <v>2466</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054663</t>
+          <t xml:space="preserve">200057628</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek Odense a/s</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,40 +13091,40 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 32</t>
+          <t xml:space="preserve">Tylvadvej 2A</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">746271, 4473222</t>
+          <t xml:space="preserve">4480225</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>2466</v>
+        <v>3911</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057628</t>
+          <t xml:space="preserve">200058806</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Odense a/s</t>
+          <t xml:space="preserve">EnergiMidt</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-04-12</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tylvadvej 2A</t>
+          <t xml:space="preserve">Fredensgade 28</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,30 +13176,30 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480225</t>
+          <t xml:space="preserve">5793356</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J176">
-        <v>3911</v>
+        <v>1346</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058806</t>
+          <t xml:space="preserve">310011917</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiMidt</t>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-12</t>
+          <t xml:space="preserve">2022-11-05</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensgade 28</t>
+          <t xml:space="preserve">Tinghusvej 4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,30 +13251,30 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5793356</t>
+          <t xml:space="preserve">5787947</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>1346</v>
+        <v>1199</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">310011917</t>
+          <t xml:space="preserve">310034028</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+          <t xml:space="preserve">Botjek Skive</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-05</t>
+          <t xml:space="preserve">2023-04-09</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,17 +13316,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusvej 4</t>
+          <t xml:space="preserve">Reberbanen 32</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787947</t>
+          <t xml:space="preserve">5724799</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="J178">
-        <v>1199</v>
+        <v>376</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034028</t>
+          <t xml:space="preserve">311138690</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Skive</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-09</t>
+          <t xml:space="preserve">2024-07-08</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reberbanen 32</t>
+          <t xml:space="preserve">Holmegaardsbakken 4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724799</t>
+          <t xml:space="preserve">100065998</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,21 +13410,21 @@
         </is>
       </c>
       <c r="J179">
-        <v>376</v>
+        <v>898</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138690</t>
+          <t xml:space="preserve">311142678</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-08</t>
+          <t xml:space="preserve">2025-10-30</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 4</t>
+          <t xml:space="preserve">Finderupsvej 9</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">100065998</t>
+          <t xml:space="preserve">7771244</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,21 +13485,21 @@
         </is>
       </c>
       <c r="J180">
-        <v>898</v>
+        <v>1089</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142678</t>
+          <t xml:space="preserve">311168902</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-30</t>
+          <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,40 +13541,40 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finderupsvej 9</t>
+          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7771244</t>
+          <t xml:space="preserve">746431, 5725289</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J181">
-        <v>1089</v>
+        <v>2061</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311168902</t>
+          <t xml:space="preserve">311169247</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-07</t>
+          <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 3B</t>
+          <t xml:space="preserve">Smed Sørensens Vej 5</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">746431, 5725289</t>
+          <t xml:space="preserve">746461, 5725289</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J182">
-        <v>2061</v>
+        <v>1794</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169247</t>
+          <t xml:space="preserve">311169248</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 5</t>
+          <t xml:space="preserve">E F Jacobsens Vej 7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">746461, 5725289</t>
+          <t xml:space="preserve">746486, 8918730</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J183">
-        <v>1794</v>
+        <v>3892</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169248</t>
+          <t xml:space="preserve">311169525</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-08</t>
+          <t xml:space="preserve">2026-04-11</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">E F Jacobsens Vej 7</t>
+          <t xml:space="preserve">Smed Sørensens Vej 6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,20 +13776,20 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">746486, 8918730</t>
+          <t xml:space="preserve">746429, 7780728</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J184">
-        <v>3892</v>
+        <v>2534</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169525</t>
+          <t xml:space="preserve">311169524</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="J185">
-        <v>2534</v>
+        <v>1249</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smed Sørensens Vej 6</t>
+          <t xml:space="preserve">Agersbækvej 15</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,40 +13926,40 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">746429, 7780728</t>
+          <t xml:space="preserve">335014</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>1249</v>
+        <v>1514</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311169524</t>
+          <t xml:space="preserve">311260256</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orbicon A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-11</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -14006,11 +14006,11 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>1514</v>
+        <v>917</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agersbækvej 15</t>
+          <t xml:space="preserve">Algade 63</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6971</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">335014</t>
+          <t xml:space="preserve">9676000</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J188">
-        <v>917</v>
+        <v>1571</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260256</t>
+          <t xml:space="preserve">311260252</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 63</t>
+          <t xml:space="preserve">Rindumvej 1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6971</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676000</t>
+          <t xml:space="preserve">8463704</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>1571</v>
+        <v>740</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260252</t>
+          <t xml:space="preserve">311267431</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14231,11 +14231,11 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J190">
-        <v>740</v>
+        <v>1407</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
-        <v>1407</v>
+        <v>8851</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14381,11 +14381,11 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J192">
-        <v>8851</v>
+        <v>3739</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14441,40 +14441,40 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rindumvej 1</t>
+          <t xml:space="preserve">Bardevej 5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463704</t>
+          <t xml:space="preserve">4487058</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>3739</v>
+        <v>2298</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267431</t>
+          <t xml:space="preserve">311267783</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bardevej 5</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487058</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,16 +14535,16 @@
         </is>
       </c>
       <c r="J194">
-        <v>2298</v>
+        <v>525</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267783</t>
+          <t xml:space="preserve">311267663</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Mellemgade 8</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">5787986</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,21 +14610,21 @@
         </is>
       </c>
       <c r="J195">
-        <v>525</v>
+        <v>2956</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267663</t>
+          <t xml:space="preserve">311378687</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2029-05-23</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J196">
-        <v>2956</v>
+        <v>1297</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
-        <v>1297</v>
+        <v>1261</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemgade 8</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5787986</t>
+          <t xml:space="preserve">338783</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>1261</v>
+        <v>749</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378687</t>
+          <t xml:space="preserve">311378684</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Vardevej 47A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,20 +14901,20 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">338783</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>749</v>
+        <v>620</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378684</t>
+          <t xml:space="preserve">311378685</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 47A</t>
+          <t xml:space="preserve">Lunden 1</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">4419661</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>620</v>
+        <v>2236</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311378685</t>
+          <t xml:space="preserve">311389424</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-23</t>
+          <t xml:space="preserve">2029-07-18</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J201">
-        <v>2236</v>
+        <v>453</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389424</t>
+          <t xml:space="preserve">311389426</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,30 +15116,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lunden 1</t>
+          <t xml:space="preserve">Søibergsvej 3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419661</t>
+          <t xml:space="preserve">5726628</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>453</v>
+        <v>1856</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389426</t>
+          <t xml:space="preserve">311389421</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J203">
-        <v>1856</v>
+        <v>2960</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J204">
-        <v>2960</v>
+        <v>1091</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J205">
-        <v>1091</v>
+        <v>380</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15431,11 +15431,11 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J206">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15506,11 +15506,11 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J207">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 3</t>
+          <t xml:space="preserve">Tøstrupvej 26</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726628</t>
+          <t xml:space="preserve">4466616</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>447</v>
+        <v>2185</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389421</t>
+          <t xml:space="preserve">311389428</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøstrupvej 26</t>
+          <t xml:space="preserve">Vardevej 45</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466616</t>
+          <t xml:space="preserve">338782</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>2185</v>
+        <v>655</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311389428</t>
+          <t xml:space="preserve">311391434</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-18</t>
+          <t xml:space="preserve">2029-08-06</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15731,11 +15731,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>655</v>
+        <v>262</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 45</t>
+          <t xml:space="preserve">Engdraget 24A</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">338782</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,21 +15810,21 @@
         </is>
       </c>
       <c r="J211">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391434</t>
+          <t xml:space="preserve">311419880</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-06</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 24A</t>
+          <t xml:space="preserve">Engdraget 26A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J212">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419880</t>
+          <t xml:space="preserve">311420217</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-01-31</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 26A</t>
+          <t xml:space="preserve">Skjernåvej 4A</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,30 +15951,30 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">337871, 337872</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420217</t>
+          <t xml:space="preserve">311424140</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-31</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skjernåvej 4A</t>
+          <t xml:space="preserve">Svinget 5</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">337871, 337872</t>
+          <t xml:space="preserve">5789756</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="J214">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424140</t>
+          <t xml:space="preserve">311491269</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2031-01-28</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J215">
-        <v>392</v>
+        <v>703</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16166,30 +16166,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 5</t>
+          <t xml:space="preserve">Centerparken 1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5789756</t>
+          <t xml:space="preserve">9701346</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J216">
-        <v>703</v>
+        <v>4482</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311491269</t>
+          <t xml:space="preserve">311552774</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-28</t>
+          <t xml:space="preserve">2031-10-04</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,17 +16241,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centerparken 1</t>
+          <t xml:space="preserve">Jægervej 13</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9701346</t>
+          <t xml:space="preserve">8256077</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>4482</v>
+        <v>1557</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552774</t>
+          <t xml:space="preserve">311554630</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-04</t>
+          <t xml:space="preserve">2031-10-12</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervej 13</t>
+          <t xml:space="preserve">Lærkevænget 1</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256077</t>
+          <t xml:space="preserve">1477015</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>1557</v>
+        <v>417</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554630</t>
+          <t xml:space="preserve">311554640</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,17 +16391,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevænget 1</t>
+          <t xml:space="preserve">Bredgade 120</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477015</t>
+          <t xml:space="preserve">7755094</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>417</v>
+        <v>1060</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554640</t>
+          <t xml:space="preserve">311555859</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-12</t>
+          <t xml:space="preserve">2031-10-18</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 120</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755094</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>1060</v>
+        <v>606</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555859</t>
+          <t xml:space="preserve">311561693</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-18</t>
+          <t xml:space="preserve">2031-11-13</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,17 +16541,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Storegade 40</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">4467758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>606</v>
+        <v>401</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561693</t>
+          <t xml:space="preserve">311599352</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-13</t>
+          <t xml:space="preserve">2032-02-10</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,17 +16616,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40</t>
+          <t xml:space="preserve">Åvænget 3A</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467758</t>
+          <t xml:space="preserve">100145225</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>401</v>
+        <v>810</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599352</t>
+          <t xml:space="preserve">311582272</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-10</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,17 +16691,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åvænget 3A</t>
+          <t xml:space="preserve">Nygade 1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">100145225</t>
+          <t xml:space="preserve">4467959</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>810</v>
+        <v>308</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582272</t>
+          <t xml:space="preserve">311598466</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 1</t>
+          <t xml:space="preserve">Midtbyvej 30</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4467959</t>
+          <t xml:space="preserve">7662602</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16785,21 +16785,21 @@
         </is>
       </c>
       <c r="J224">
-        <v>308</v>
+        <v>1817</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598466</t>
+          <t xml:space="preserve">311650708</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">MST-Bygtjek ApS</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,40 +16841,40 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtbyvej 30</t>
+          <t xml:space="preserve">Ranunkelvej 11A</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7662602</t>
+          <t xml:space="preserve">5790131, 100782857</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J225">
-        <v>1817</v>
+        <v>414</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650708</t>
+          <t xml:space="preserve">311689382</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">MST-Bygtjek ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,40 +16916,40 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 11A</t>
+          <t xml:space="preserve">Skolebakken 20</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5790131, 100782857</t>
+          <t xml:space="preserve">746445, 4419703</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J226">
-        <v>414</v>
+        <v>3326</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689382</t>
+          <t xml:space="preserve">311883390</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2036-02-21</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,30 +16991,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 20</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">746445, 4419703</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J227">
-        <v>3326</v>
+        <v>1345</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883390</t>
+          <t xml:space="preserve">311886105</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-21</t>
+          <t xml:space="preserve">2036-03-08</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17081,15 +17081,15 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J228">
-        <v>1345</v>
+        <v>2810</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886105</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17156,15 +17156,15 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J229">
-        <v>2810</v>
+        <v>1725</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311886107</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17231,15 +17231,15 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J230">
-        <v>1725</v>
+        <v>1360</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886107</t>
+          <t xml:space="preserve">311886098</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Klostervej 85</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,21 +17310,21 @@
         </is>
       </c>
       <c r="J231">
-        <v>1360</v>
+        <v>703</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886098</t>
+          <t xml:space="preserve">311889055</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-08</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,40 +17366,40 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 85</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>703</v>
+        <v>766</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311889055</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,30 +17441,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>766</v>
+        <v>2123</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J234">
-        <v>2123</v>
+        <v>915</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J235">
-        <v>915</v>
+        <v>616</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J236">
-        <v>616</v>
+        <v>1810</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17741,35 +17741,35 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">746506, 4477641</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>1810</v>
+        <v>2072</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311892347</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Ågade 12</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">746506, 4477641</t>
+          <t xml:space="preserve">9221920</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,16 +17835,16 @@
         </is>
       </c>
       <c r="J238">
-        <v>2072</v>
+        <v>729</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892347</t>
+          <t xml:space="preserve">311892262</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 12</t>
+          <t xml:space="preserve">Ågade 14</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J239">
@@ -17966,17 +17966,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 14</t>
+          <t xml:space="preserve">Badevej 17A</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">9221920</t>
+          <t xml:space="preserve">4421290, 100992804</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,21 +17985,21 @@
         </is>
       </c>
       <c r="J240">
-        <v>729</v>
+        <v>370</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892262</t>
+          <t xml:space="preserve">311900271</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-05-10</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,40 +18041,40 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Badevej 17A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421290, 100992804</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J241">
-        <v>370</v>
+        <v>788</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900271</t>
+          <t xml:space="preserve">311929041</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bedre Bolig Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-10</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,40 +18116,40 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J242">
-        <v>788</v>
+        <v>735</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929041</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
